--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08082026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="08082026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AZ16"/>
+  <dimension ref="A2:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -537,9 +537,6 @@
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
     <col width="9" customWidth="1" min="49" max="49"/>
-    <col width="9" customWidth="1" min="50" max="50"/>
-    <col width="9" customWidth="1" min="51" max="51"/>
-    <col width="9" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -597,11 +594,8 @@
       <c r="AR3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="AU3" s="3" t="n">
+      <c r="AU3" s="4" t="n">
         <v>46241</v>
-      </c>
-      <c r="AX3" s="4" t="n">
-        <v>46242</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -837,32 +831,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AU4" s="5" t="inlineStr">
+      <c r="AU4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="AV4" s="5" t="inlineStr">
+      <c r="AV4" s="6" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AW4" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="AX4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEW SALES </t>
-        </is>
-      </c>
-      <c r="AY4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL SOLD</t>
-        </is>
-      </c>
-      <c r="AZ4" s="6" t="inlineStr">
+      <c r="AW4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1040,26 +1019,15 @@
         <f>AS5/$E$5</f>
         <v/>
       </c>
-      <c r="AU5" s="9">
+      <c r="AU5" s="11">
         <f>AV5-AS5</f>
         <v/>
       </c>
-      <c r="AV5" s="9" t="n">
+      <c r="AV5" s="11" t="n">
         <v>319</v>
       </c>
-      <c r="AW5" s="10">
+      <c r="AW5" s="12">
         <f>AV5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AX5" s="11">
-        <f>AY5-AV5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="11" t="n">
-        <v>321</v>
-      </c>
-      <c r="AZ5" s="12">
-        <f>AY5/$E$5</f>
         <v/>
       </c>
     </row>
@@ -1236,26 +1204,15 @@
         <f>AS6/$E$6</f>
         <v/>
       </c>
-      <c r="AU6" s="9">
+      <c r="AU6" s="11">
         <f>AV6-AS6</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="n">
+      <c r="AV6" s="11" t="n">
         <v>112</v>
       </c>
-      <c r="AW6" s="10">
+      <c r="AW6" s="12">
         <f>AV6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AX6" s="11">
-        <f>AY6-AV6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="11" t="n">
-        <v>113</v>
-      </c>
-      <c r="AZ6" s="12">
-        <f>AY6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1431,26 +1388,15 @@
         <f>AS7/$E$7</f>
         <v/>
       </c>
-      <c r="AU7" s="9">
+      <c r="AU7" s="11">
         <f>AV7-AS7</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="n">
+      <c r="AV7" s="11" t="n">
         <v>985</v>
       </c>
-      <c r="AW7" s="10">
+      <c r="AW7" s="12">
         <f>AV7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AX7" s="11">
-        <f>AY7-AV7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="11" t="n">
-        <v>986</v>
-      </c>
-      <c r="AZ7" s="12">
-        <f>AY7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1627,26 +1573,15 @@
         <f>AS8/$E$8</f>
         <v/>
       </c>
-      <c r="AU8" s="9">
+      <c r="AU8" s="11">
         <f>AV8-AS8</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="n">
+      <c r="AV8" s="11" t="n">
         <v>1119</v>
       </c>
-      <c r="AW8" s="10">
+      <c r="AW8" s="12">
         <f>AV8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AX8" s="11">
-        <f>AY8-AV8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="11" t="n">
-        <v>1119</v>
-      </c>
-      <c r="AZ8" s="12">
-        <f>AY8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1823,26 +1758,15 @@
         <f>AS9/$E$9</f>
         <v/>
       </c>
-      <c r="AU9" s="9">
+      <c r="AU9" s="11">
         <f>AV9-AS9</f>
         <v/>
       </c>
-      <c r="AV9" s="9" t="n">
+      <c r="AV9" s="11" t="n">
         <v>491</v>
       </c>
-      <c r="AW9" s="10">
+      <c r="AW9" s="12">
         <f>AV9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AX9" s="11">
-        <f>AY9-AV9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="11" t="n">
-        <v>491</v>
-      </c>
-      <c r="AZ9" s="12">
-        <f>AY9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -2018,26 +1942,15 @@
         <f>AS10/$E$10</f>
         <v/>
       </c>
-      <c r="AU10" s="9">
+      <c r="AU10" s="11">
         <f>AV10-AS10</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="n">
+      <c r="AV10" s="11" t="n">
         <v>465</v>
       </c>
-      <c r="AW10" s="10">
+      <c r="AW10" s="12">
         <f>AV10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AX10" s="11">
-        <f>AY10-AV10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="11" t="n">
-        <v>466</v>
-      </c>
-      <c r="AZ10" s="12">
-        <f>AY10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2213,26 +2126,15 @@
         <f>AS11/$E$11</f>
         <v/>
       </c>
-      <c r="AU11" s="9">
+      <c r="AU11" s="11">
         <f>AV11-AS11</f>
         <v/>
       </c>
-      <c r="AV11" s="9" t="n">
+      <c r="AV11" s="11" t="n">
         <v>235</v>
       </c>
-      <c r="AW11" s="10">
+      <c r="AW11" s="12">
         <f>AV11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AX11" s="11">
-        <f>AY11-AV11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="11" t="n">
-        <v>235</v>
-      </c>
-      <c r="AZ11" s="12">
-        <f>AY11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2409,26 +2311,15 @@
         <f>AS12/$E$12</f>
         <v/>
       </c>
-      <c r="AU12" s="9">
+      <c r="AU12" s="11">
         <f>AV12-AS12</f>
         <v/>
       </c>
-      <c r="AV12" s="9" t="n">
+      <c r="AV12" s="11" t="n">
         <v>608</v>
       </c>
-      <c r="AW12" s="10">
+      <c r="AW12" s="12">
         <f>AV12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AX12" s="11">
-        <f>AY12-AV12</f>
-        <v/>
-      </c>
-      <c r="AY12" s="11" t="n">
-        <v>609</v>
-      </c>
-      <c r="AZ12" s="12">
-        <f>AY12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2604,26 +2495,15 @@
         <f>AS13/$E$13</f>
         <v/>
       </c>
-      <c r="AU13" s="9">
+      <c r="AU13" s="11">
         <f>AV13-AS13</f>
         <v/>
       </c>
-      <c r="AV13" s="9" t="n">
+      <c r="AV13" s="11" t="n">
         <v>1139</v>
       </c>
-      <c r="AW13" s="10">
+      <c r="AW13" s="12">
         <f>AV13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AX13" s="11">
-        <f>AY13-AV13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="11" t="n">
-        <v>1140</v>
-      </c>
-      <c r="AZ13" s="12">
-        <f>AY13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2799,26 +2679,15 @@
         <f>AS14/$E$14</f>
         <v/>
       </c>
-      <c r="AU14" s="9">
+      <c r="AU14" s="11">
         <f>AV14-AS14</f>
         <v/>
       </c>
-      <c r="AV14" s="9" t="n">
+      <c r="AV14" s="11" t="n">
         <v>124</v>
       </c>
-      <c r="AW14" s="10">
+      <c r="AW14" s="12">
         <f>AV14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AX14" s="11">
-        <f>AY14-AV14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="11" t="n">
-        <v>124</v>
-      </c>
-      <c r="AZ14" s="12">
-        <f>AY14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -2930,26 +2799,15 @@
         <f>AS15/$E$15</f>
         <v/>
       </c>
-      <c r="AU15" s="9">
+      <c r="AU15" s="11">
         <f>AV15-AS15</f>
         <v/>
       </c>
-      <c r="AV15" s="9" t="n">
+      <c r="AV15" s="11" t="n">
         <v>659</v>
       </c>
-      <c r="AW15" s="10">
+      <c r="AW15" s="12">
         <f>AV15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AX15" s="11">
-        <f>AY15-AV15</f>
-        <v/>
-      </c>
-      <c r="AY15" s="11" t="n">
-        <v>659</v>
-      </c>
-      <c r="AZ15" s="12">
-        <f>AY15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -3121,31 +2979,20 @@
         <f>AS16/$E$16</f>
         <v/>
       </c>
-      <c r="AU16" s="9">
+      <c r="AU16" s="11">
         <f>AV16-AS16</f>
         <v/>
       </c>
-      <c r="AV16" s="9" t="n">
+      <c r="AV16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="AW16" s="10">
+      <c r="AW16" s="12">
         <f>AV16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AX16" s="11">
-        <f>AY16-AV16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="12">
-        <f>AY16/$E$16</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
     <mergeCell ref="W3:Y3"/>
@@ -3154,7 +3001,6 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="AC3:AE3"/>
     <mergeCell ref="AF3:AH3"/>
-    <mergeCell ref="AX3:AZ3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="Z3:AB3"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AW16"/>
+  <dimension ref="A2:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -853,183 +853,66 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>M AURORA</t>
+          <t>RESIDENSI WARISAN SALAK SELATAN</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>13262-2</t>
+          <t>31202-1</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>MAJORLAND DEVELOPMENT SDN BHD</t>
+          <t>EC VANTAGE SDN. BHD.</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>1544</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="G5" s="10">
-        <f>F5/$E$5</f>
-        <v/>
-      </c>
-      <c r="H5" s="9">
-        <f>I5-F5</f>
-        <v/>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>109</v>
-      </c>
-      <c r="J5" s="10">
-        <f>I5/$E$5</f>
-        <v/>
-      </c>
-      <c r="K5" s="9">
-        <f>L5-I5</f>
-        <v/>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>123</v>
-      </c>
-      <c r="M5" s="10">
-        <f>L5/$E$5</f>
-        <v/>
-      </c>
-      <c r="N5" s="9">
-        <f>O5-L5</f>
-        <v/>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>138</v>
-      </c>
-      <c r="P5" s="10">
-        <f>O5/$E$5</f>
-        <v/>
-      </c>
-      <c r="Q5" s="9">
-        <f>R5-O5</f>
-        <v/>
-      </c>
-      <c r="R5" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="S5" s="10">
-        <f>R5/$E$5</f>
-        <v/>
-      </c>
-      <c r="T5" s="9">
-        <f>U5-R5</f>
-        <v/>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>191</v>
-      </c>
-      <c r="V5" s="10">
-        <f>U5/$E$5</f>
-        <v/>
-      </c>
-      <c r="W5" s="9">
-        <f>X5-U5</f>
-        <v/>
-      </c>
-      <c r="X5" s="9" t="n">
-        <v>213</v>
-      </c>
-      <c r="Y5" s="10">
-        <f>X5/$E$5</f>
-        <v/>
-      </c>
-      <c r="Z5" s="9">
-        <f>AA5-X5</f>
-        <v/>
-      </c>
-      <c r="AA5" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB5" s="10">
-        <f>AA5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="9">
-        <f>AD5-AA5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n">
-        <v>231</v>
-      </c>
-      <c r="AE5" s="10">
-        <f>AD5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AF5" s="9">
-        <f>AG5-AD5</f>
-        <v/>
-      </c>
-      <c r="AG5" s="9" t="n">
-        <v>241</v>
-      </c>
-      <c r="AH5" s="10">
-        <f>AG5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AI5" s="9">
-        <f>AJ5-AG5</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="9" t="n">
-        <v>247</v>
-      </c>
-      <c r="AK5" s="10">
-        <f>AJ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AL5" s="9">
-        <f>AM5-AJ5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n">
-        <v>269</v>
-      </c>
-      <c r="AN5" s="10">
-        <f>AM5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AO5" s="9">
-        <f>AP5-AM5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="9" t="n">
-        <v>285</v>
-      </c>
-      <c r="AQ5" s="10">
-        <f>AP5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AR5" s="9">
-        <f>AS5-AP5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n">
-        <v>306</v>
-      </c>
-      <c r="AT5" s="10">
-        <f>AS5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AU5" s="11">
-        <f>AV5-AS5</f>
-        <v/>
-      </c>
-      <c r="AV5" s="11" t="n">
-        <v>319</v>
-      </c>
-      <c r="AW5" s="12">
-        <f>AV5/$E$5</f>
-        <v/>
-      </c>
+        <v>1310</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="10" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="10" t="n"/>
+      <c r="AC5" s="9" t="n"/>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AF5" s="9" t="n"/>
+      <c r="AG5" s="9" t="n"/>
+      <c r="AH5" s="10" t="n"/>
+      <c r="AI5" s="9" t="n"/>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="10" t="n"/>
+      <c r="AL5" s="9" t="n"/>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="10" t="n"/>
+      <c r="AO5" s="9" t="n"/>
+      <c r="AP5" s="9" t="n"/>
+      <c r="AQ5" s="10" t="n"/>
+      <c r="AR5" s="9" t="n"/>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="10" t="n"/>
+      <c r="AU5" s="11" t="n"/>
+      <c r="AV5" s="11" t="n"/>
+      <c r="AW5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1037,25 +920,24 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>ARTE STAR 
-MILANO</t>
+          <t>M AURORA</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>30590-2</t>
+          <t>13262-2</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>SURIAMEGA DEVELOPMENT</t>
+          <t>MAJORLAND DEVELOPMENT SDN BHD</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>996</v>
+        <v>1544</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="G6" s="10">
         <f>F6/$E$6</f>
@@ -1066,7 +948,7 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="J6" s="10">
         <f>I6/$E$6</f>
@@ -1077,7 +959,7 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="M6" s="10">
         <f>L6/$E$6</f>
@@ -1088,7 +970,7 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="P6" s="10">
         <f>O6/$E$6</f>
@@ -1099,7 +981,7 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="S6" s="10">
         <f>R6/$E$6</f>
@@ -1110,7 +992,7 @@
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="V6" s="10">
         <f>U6/$E$6</f>
@@ -1121,7 +1003,7 @@
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="Y6" s="10">
         <f>X6/$E$6</f>
@@ -1132,7 +1014,7 @@
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>73</v>
+        <v>220</v>
       </c>
       <c r="AB6" s="10">
         <f>AA6/$E$6</f>
@@ -1143,7 +1025,7 @@
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="AE6" s="10">
         <f>AD6/$E$6</f>
@@ -1154,7 +1036,7 @@
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AH6" s="10">
         <f>AG6/$E$6</f>
@@ -1165,7 +1047,7 @@
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AK6" s="10">
         <f>AJ6/$E$6</f>
@@ -1176,7 +1058,7 @@
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>94</v>
+        <v>269</v>
       </c>
       <c r="AN6" s="10">
         <f>AM6/$E$6</f>
@@ -1187,7 +1069,7 @@
         <v/>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="AQ6" s="10">
         <f>AP6/$E$6</f>
@@ -1198,7 +1080,7 @@
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>106</v>
+        <v>306</v>
       </c>
       <c r="AT6" s="10">
         <f>AS6/$E$6</f>
@@ -1209,7 +1091,7 @@
         <v/>
       </c>
       <c r="AV6" s="11" t="n">
-        <v>112</v>
+        <v>319</v>
       </c>
       <c r="AW6" s="12">
         <f>AV6/$E$6</f>
@@ -1222,24 +1104,25 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> M ASPIRA</t>
+          <t>ARTE STAR 
+MILANO</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>5911-33</t>
+          <t>30590-2</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>MAH SING GROUP BERHAD</t>
+          <t>SURIAMEGA DEVELOPMENT</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>1618</v>
+        <v>996</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>792</v>
+        <v>46</v>
       </c>
       <c r="G7" s="10">
         <f>F7/$E$7</f>
@@ -1250,7 +1133,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>808</v>
+        <v>52</v>
       </c>
       <c r="J7" s="10">
         <f>I7/$E$7</f>
@@ -1261,7 +1144,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>818</v>
+        <v>54</v>
       </c>
       <c r="M7" s="10">
         <f>L7/$E$7</f>
@@ -1272,7 +1155,7 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>837</v>
+        <v>58</v>
       </c>
       <c r="P7" s="10">
         <f>O7/$E$7</f>
@@ -1283,7 +1166,7 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>854</v>
+        <v>61</v>
       </c>
       <c r="S7" s="10">
         <f>R7/$E$7</f>
@@ -1294,7 +1177,7 @@
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>874</v>
+        <v>67</v>
       </c>
       <c r="V7" s="10">
         <f>U7/$E$7</f>
@@ -1305,7 +1188,7 @@
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>878</v>
+        <v>67</v>
       </c>
       <c r="Y7" s="10">
         <f>X7/$E$7</f>
@@ -1316,7 +1199,7 @@
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>885</v>
+        <v>73</v>
       </c>
       <c r="AB7" s="10">
         <f>AA7/$E$7</f>
@@ -1327,7 +1210,7 @@
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>892</v>
+        <v>74</v>
       </c>
       <c r="AE7" s="10">
         <f>AD7/$E$7</f>
@@ -1338,7 +1221,7 @@
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>907</v>
+        <v>78</v>
       </c>
       <c r="AH7" s="10">
         <f>AG7/$E$7</f>
@@ -1349,7 +1232,7 @@
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>922</v>
+        <v>81</v>
       </c>
       <c r="AK7" s="10">
         <f>AJ7/$E$7</f>
@@ -1360,7 +1243,7 @@
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>951</v>
+        <v>94</v>
       </c>
       <c r="AN7" s="10">
         <f>AM7/$E$7</f>
@@ -1371,7 +1254,7 @@
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>965</v>
+        <v>102</v>
       </c>
       <c r="AQ7" s="10">
         <f>AP7/$E$7</f>
@@ -1382,7 +1265,7 @@
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>976</v>
+        <v>106</v>
       </c>
       <c r="AT7" s="10">
         <f>AS7/$E$7</f>
@@ -1393,7 +1276,7 @@
         <v/>
       </c>
       <c r="AV7" s="11" t="n">
-        <v>985</v>
+        <v>112</v>
       </c>
       <c r="AW7" s="12">
         <f>AV7/$E$7</f>
@@ -1406,25 +1289,24 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI DESA TIMUR
-A DESA</t>
+          <t xml:space="preserve"> M ASPIRA</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>30363-2</t>
+          <t>5911-33</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>FITRAH RESOURCES SDN BHD</t>
+          <t>MAH SING GROUP BERHAD</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>1218</v>
+        <v>1618</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>1091</v>
+        <v>792</v>
       </c>
       <c r="G8" s="10">
         <f>F8/$E$8</f>
@@ -1435,7 +1317,7 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="J8" s="10">
         <f>I8/$E$8</f>
@@ -1446,7 +1328,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1093</v>
+        <v>818</v>
       </c>
       <c r="M8" s="10">
         <f>L8/$E$8</f>
@@ -1457,7 +1339,7 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>1095</v>
+        <v>837</v>
       </c>
       <c r="P8" s="10">
         <f>O8/$E$8</f>
@@ -1468,7 +1350,7 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>1096</v>
+        <v>854</v>
       </c>
       <c r="S8" s="10">
         <f>R8/$E$8</f>
@@ -1479,7 +1361,7 @@
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>1100</v>
+        <v>874</v>
       </c>
       <c r="V8" s="10">
         <f>U8/$E$8</f>
@@ -1490,7 +1372,7 @@
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>1102</v>
+        <v>878</v>
       </c>
       <c r="Y8" s="10">
         <f>X8/$E$8</f>
@@ -1501,7 +1383,7 @@
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>1106</v>
+        <v>885</v>
       </c>
       <c r="AB8" s="10">
         <f>AA8/$E$8</f>
@@ -1512,7 +1394,7 @@
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>1107</v>
+        <v>892</v>
       </c>
       <c r="AE8" s="10">
         <f>AD8/$E$8</f>
@@ -1523,7 +1405,7 @@
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>1109</v>
+        <v>907</v>
       </c>
       <c r="AH8" s="10">
         <f>AG8/$E$8</f>
@@ -1534,7 +1416,7 @@
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>1111</v>
+        <v>922</v>
       </c>
       <c r="AK8" s="10">
         <f>AJ8/$E$8</f>
@@ -1545,7 +1427,7 @@
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>1116</v>
+        <v>951</v>
       </c>
       <c r="AN8" s="10">
         <f>AM8/$E$8</f>
@@ -1556,7 +1438,7 @@
         <v/>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>1117</v>
+        <v>965</v>
       </c>
       <c r="AQ8" s="10">
         <f>AP8/$E$8</f>
@@ -1567,7 +1449,7 @@
         <v/>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>1117</v>
+        <v>976</v>
       </c>
       <c r="AT8" s="10">
         <f>AS8/$E$8</f>
@@ -1578,7 +1460,7 @@
         <v/>
       </c>
       <c r="AV8" s="11" t="n">
-        <v>1119</v>
+        <v>985</v>
       </c>
       <c r="AW8" s="12">
         <f>AV8/$E$8</f>
@@ -1591,25 +1473,25 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>RADIUM ARENA
-RESIDENSI RADIUM</t>
+          <t>RESIDENSI DESA TIMUR
+A DESA</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>30821-1</t>
+          <t>30363-2</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>RADIUM GLOBAL SDN BHD</t>
+          <t>FITRAH RESOURCES SDN BHD</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>988</v>
+        <v>1218</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>446</v>
+        <v>1091</v>
       </c>
       <c r="G9" s="10">
         <f>F9/$E$9</f>
@@ -1631,7 +1513,7 @@
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>447</v>
+        <v>1093</v>
       </c>
       <c r="M9" s="10">
         <f>L9/$E$9</f>
@@ -1642,7 +1524,7 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>457</v>
+        <v>1095</v>
       </c>
       <c r="P9" s="10">
         <f>O9/$E$9</f>
@@ -1653,7 +1535,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>458</v>
+        <v>1096</v>
       </c>
       <c r="S9" s="10">
         <f>R9/$E$9</f>
@@ -1664,7 +1546,7 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>460</v>
+        <v>1100</v>
       </c>
       <c r="V9" s="10">
         <f>U9/$E$9</f>
@@ -1675,7 +1557,7 @@
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>460</v>
+        <v>1102</v>
       </c>
       <c r="Y9" s="10">
         <f>X9/$E$9</f>
@@ -1686,7 +1568,7 @@
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>462</v>
+        <v>1106</v>
       </c>
       <c r="AB9" s="10">
         <f>AA9/$E$9</f>
@@ -1697,7 +1579,7 @@
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>462</v>
+        <v>1107</v>
       </c>
       <c r="AE9" s="10">
         <f>AD9/$E$9</f>
@@ -1708,7 +1590,7 @@
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>463</v>
+        <v>1109</v>
       </c>
       <c r="AH9" s="10">
         <f>AG9/$E$9</f>
@@ -1719,7 +1601,7 @@
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>464</v>
+        <v>1111</v>
       </c>
       <c r="AK9" s="10">
         <f>AJ9/$E$9</f>
@@ -1730,7 +1612,7 @@
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>472</v>
+        <v>1116</v>
       </c>
       <c r="AN9" s="10">
         <f>AM9/$E$9</f>
@@ -1741,7 +1623,7 @@
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>475</v>
+        <v>1117</v>
       </c>
       <c r="AQ9" s="10">
         <f>AP9/$E$9</f>
@@ -1752,7 +1634,7 @@
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>485</v>
+        <v>1117</v>
       </c>
       <c r="AT9" s="10">
         <f>AS9/$E$9</f>
@@ -1763,7 +1645,7 @@
         <v/>
       </c>
       <c r="AV9" s="11" t="n">
-        <v>491</v>
+        <v>1119</v>
       </c>
       <c r="AW9" s="12">
         <f>AV9/$E$9</f>
@@ -1776,24 +1658,25 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI AMBIEN</t>
+          <t>RADIUM ARENA
+RESIDENSI RADIUM</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>30366-1</t>
+          <t>30821-1</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>FAITHVIEW RESOURCES SDN BHD</t>
+          <t>RADIUM GLOBAL SDN BHD</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>482</v>
+        <v>988</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="G10" s="10">
         <f>F10/$E$10</f>
@@ -1804,7 +1687,7 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="J10" s="10">
         <f>I10/$E$10</f>
@@ -1815,7 +1698,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="M10" s="10">
         <f>L10/$E$10</f>
@@ -1837,7 +1720,7 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S10" s="10">
         <f>R10/$E$10</f>
@@ -1848,7 +1731,7 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="V10" s="10">
         <f>U10/$E$10</f>
@@ -1859,7 +1742,7 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Y10" s="10">
         <f>X10/$E$10</f>
@@ -1870,7 +1753,7 @@
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AB10" s="10">
         <f>AA10/$E$10</f>
@@ -1881,7 +1764,7 @@
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AE10" s="10">
         <f>AD10/$E$10</f>
@@ -1892,7 +1775,7 @@
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AH10" s="10">
         <f>AG10/$E$10</f>
@@ -1914,7 +1797,7 @@
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="AN10" s="10">
         <f>AM10/$E$10</f>
@@ -1925,7 +1808,7 @@
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="AQ10" s="10">
         <f>AP10/$E$10</f>
@@ -1936,7 +1819,7 @@
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="AT10" s="10">
         <f>AS10/$E$10</f>
@@ -1947,7 +1830,7 @@
         <v/>
       </c>
       <c r="AV10" s="11" t="n">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="AW10" s="12">
         <f>AV10/$E$10</f>
@@ -1960,24 +1843,24 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI HANA</t>
+          <t>RESIDENSI AMBIEN</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>13074-4</t>
+          <t>30366-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>NATURAL DOMAIN SDN BHD</t>
+          <t>FAITHVIEW RESOURCES SDN BHD</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>299</v>
+        <v>482</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>234</v>
+        <v>452</v>
       </c>
       <c r="G11" s="10">
         <f>F11/$E$11</f>
@@ -1988,7 +1871,7 @@
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="J11" s="10">
         <f>I11/$E$11</f>
@@ -1999,7 +1882,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>235</v>
+        <v>456</v>
       </c>
       <c r="M11" s="10">
         <f>L11/$E$11</f>
@@ -2010,7 +1893,7 @@
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="P11" s="10">
         <f>O11/$E$11</f>
@@ -2021,7 +1904,7 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>236</v>
+        <v>459</v>
       </c>
       <c r="S11" s="10">
         <f>R11/$E$11</f>
@@ -2032,7 +1915,7 @@
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>236</v>
+        <v>461</v>
       </c>
       <c r="V11" s="10">
         <f>U11/$E$11</f>
@@ -2043,7 +1926,7 @@
         <v/>
       </c>
       <c r="X11" s="9" t="n">
-        <v>236</v>
+        <v>462</v>
       </c>
       <c r="Y11" s="10">
         <f>X11/$E$11</f>
@@ -2054,7 +1937,7 @@
         <v/>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>236</v>
+        <v>463</v>
       </c>
       <c r="AB11" s="10">
         <f>AA11/$E$11</f>
@@ -2065,7 +1948,7 @@
         <v/>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>236</v>
+        <v>463</v>
       </c>
       <c r="AE11" s="10">
         <f>AD11/$E$11</f>
@@ -2076,7 +1959,7 @@
         <v/>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="AH11" s="10">
         <f>AG11/$E$11</f>
@@ -2087,7 +1970,7 @@
         <v/>
       </c>
       <c r="AJ11" s="9" t="n">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="AK11" s="10">
         <f>AJ11/$E$11</f>
@@ -2098,7 +1981,7 @@
         <v/>
       </c>
       <c r="AM11" s="9" t="n">
-        <v>234</v>
+        <v>465</v>
       </c>
       <c r="AN11" s="10">
         <f>AM11/$E$11</f>
@@ -2109,7 +1992,7 @@
         <v/>
       </c>
       <c r="AP11" s="9" t="n">
-        <v>234</v>
+        <v>465</v>
       </c>
       <c r="AQ11" s="10">
         <f>AP11/$E$11</f>
@@ -2120,7 +2003,7 @@
         <v/>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>234</v>
+        <v>465</v>
       </c>
       <c r="AT11" s="10">
         <f>AS11/$E$11</f>
@@ -2131,7 +2014,7 @@
         <v/>
       </c>
       <c r="AV11" s="11" t="n">
-        <v>235</v>
+        <v>465</v>
       </c>
       <c r="AW11" s="12">
         <f>AV11/$E$11</f>
@@ -2144,25 +2027,24 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI
-SUNWAY COCHRANE</t>
+          <t>RESIDENSI HANA</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>8824-5</t>
+          <t>13074-4</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>SUNWAY COCHRANE SDN BHD</t>
+          <t>NATURAL DOMAIN SDN BHD</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1296</v>
+        <v>299</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>379</v>
+        <v>234</v>
       </c>
       <c r="G12" s="10">
         <f>F12/$E$12</f>
@@ -2184,7 +2066,7 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>381</v>
+        <v>235</v>
       </c>
       <c r="M12" s="10">
         <f>L12/$E$12</f>
@@ -2195,7 +2077,7 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="P12" s="10">
         <f>O12/$E$12</f>
@@ -2206,7 +2088,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>389</v>
+        <v>236</v>
       </c>
       <c r="S12" s="10">
         <f>R12/$E$12</f>
@@ -2217,7 +2099,7 @@
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>397</v>
+        <v>236</v>
       </c>
       <c r="V12" s="10">
         <f>U12/$E$12</f>
@@ -2228,7 +2110,7 @@
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>401</v>
+        <v>236</v>
       </c>
       <c r="Y12" s="10">
         <f>X12/$E$12</f>
@@ -2239,7 +2121,7 @@
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>412</v>
+        <v>236</v>
       </c>
       <c r="AB12" s="10">
         <f>AA12/$E$12</f>
@@ -2250,7 +2132,7 @@
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>421</v>
+        <v>236</v>
       </c>
       <c r="AE12" s="10">
         <f>AD12/$E$12</f>
@@ -2261,7 +2143,7 @@
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>433</v>
+        <v>236</v>
       </c>
       <c r="AH12" s="10">
         <f>AG12/$E$12</f>
@@ -2272,7 +2154,7 @@
         <v/>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>460</v>
+        <v>236</v>
       </c>
       <c r="AK12" s="10">
         <f>AJ12/$E$12</f>
@@ -2283,7 +2165,7 @@
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>544</v>
+        <v>234</v>
       </c>
       <c r="AN12" s="10">
         <f>AM12/$E$12</f>
@@ -2294,7 +2176,7 @@
         <v/>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>573</v>
+        <v>234</v>
       </c>
       <c r="AQ12" s="10">
         <f>AP12/$E$12</f>
@@ -2305,7 +2187,7 @@
         <v/>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>591</v>
+        <v>234</v>
       </c>
       <c r="AT12" s="10">
         <f>AS12/$E$12</f>
@@ -2316,7 +2198,7 @@
         <v/>
       </c>
       <c r="AV12" s="11" t="n">
-        <v>608</v>
+        <v>235</v>
       </c>
       <c r="AW12" s="12">
         <f>AV12/$E$12</f>
@@ -2329,24 +2211,25 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI PLATINUM SAUJANA VIOLET 2 (PSV2)</t>
+          <t>RESIDENSI
+SUNWAY COCHRANE</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>20253-3</t>
+          <t>8824-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>PEMBINAAN SERTA HEBAT SDN.BHD</t>
+          <t>SUNWAY COCHRANE SDN BHD</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1500</v>
+        <v>1296</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G13" s="10">
         <f>F13/$E$13</f>
@@ -2368,7 +2251,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="M13" s="10">
         <f>L13/$E$13</f>
@@ -2379,7 +2262,7 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="P13" s="10">
         <f>O13/$E$13</f>
@@ -2390,7 +2273,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="S13" s="10">
         <f>R13/$E$13</f>
@@ -2401,7 +2284,7 @@
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="V13" s="10">
         <f>U13/$E$13</f>
@@ -2412,7 +2295,7 @@
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>1086</v>
+        <v>401</v>
       </c>
       <c r="Y13" s="10">
         <f>X13/$E$13</f>
@@ -2423,7 +2306,7 @@
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>1096</v>
+        <v>412</v>
       </c>
       <c r="AB13" s="10">
         <f>AA13/$E$13</f>
@@ -2434,7 +2317,7 @@
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>1100</v>
+        <v>421</v>
       </c>
       <c r="AE13" s="10">
         <f>AD13/$E$13</f>
@@ -2445,7 +2328,7 @@
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>1110</v>
+        <v>433</v>
       </c>
       <c r="AH13" s="10">
         <f>AG13/$E$13</f>
@@ -2456,7 +2339,7 @@
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>1115</v>
+        <v>460</v>
       </c>
       <c r="AK13" s="10">
         <f>AJ13/$E$13</f>
@@ -2467,7 +2350,7 @@
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>1126</v>
+        <v>544</v>
       </c>
       <c r="AN13" s="10">
         <f>AM13/$E$13</f>
@@ -2478,7 +2361,7 @@
         <v/>
       </c>
       <c r="AP13" s="9" t="n">
-        <v>1129</v>
+        <v>573</v>
       </c>
       <c r="AQ13" s="10">
         <f>AP13/$E$13</f>
@@ -2489,7 +2372,7 @@
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>1135</v>
+        <v>591</v>
       </c>
       <c r="AT13" s="10">
         <f>AS13/$E$13</f>
@@ -2500,7 +2383,7 @@
         <v/>
       </c>
       <c r="AV13" s="11" t="n">
-        <v>1139</v>
+        <v>608</v>
       </c>
       <c r="AW13" s="12">
         <f>AV13/$E$13</f>
@@ -2513,21 +2396,21 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI VERIDIAN</t>
+          <t>RESIDENSI PLATINUM SAUJANA VIOLET 2 (PSV2)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>30876-1</t>
+          <t>20253-3</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>PERUMAHAN MASTERON SDN BHD</t>
+          <t>PEMBINAAN SERTA HEBAT SDN.BHD</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>551</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0</v>
@@ -2574,7 +2457,7 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="S14" s="10">
         <f>R14/$E$14</f>
@@ -2585,7 +2468,7 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="V14" s="10">
         <f>U14/$E$14</f>
@@ -2596,7 +2479,7 @@
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>76</v>
+        <v>1086</v>
       </c>
       <c r="Y14" s="10">
         <f>X14/$E$14</f>
@@ -2607,7 +2490,7 @@
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>79</v>
+        <v>1096</v>
       </c>
       <c r="AB14" s="10">
         <f>AA14/$E$14</f>
@@ -2618,7 +2501,7 @@
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>82</v>
+        <v>1100</v>
       </c>
       <c r="AE14" s="10">
         <f>AD14/$E$14</f>
@@ -2629,7 +2512,7 @@
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>86</v>
+        <v>1110</v>
       </c>
       <c r="AH14" s="10">
         <f>AG14/$E$14</f>
@@ -2640,7 +2523,7 @@
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>96</v>
+        <v>1115</v>
       </c>
       <c r="AK14" s="10">
         <f>AJ14/$E$14</f>
@@ -2651,7 +2534,7 @@
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>118</v>
+        <v>1126</v>
       </c>
       <c r="AN14" s="10">
         <f>AM14/$E$14</f>
@@ -2662,7 +2545,7 @@
         <v/>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>121</v>
+        <v>1129</v>
       </c>
       <c r="AQ14" s="10">
         <f>AP14/$E$14</f>
@@ -2673,7 +2556,7 @@
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>121</v>
+        <v>1135</v>
       </c>
       <c r="AT14" s="10">
         <f>AS14/$E$14</f>
@@ -2684,7 +2567,7 @@
         <v/>
       </c>
       <c r="AV14" s="11" t="n">
-        <v>124</v>
+        <v>1139</v>
       </c>
       <c r="AW14" s="12">
         <f>AV14/$E$14</f>
@@ -2697,21 +2580,21 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI AURUM</t>
+          <t>RESIDENSI VERIDIAN</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>30250-2</t>
+          <t>30876-1</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>AMBER HOMES SRI PETALING SDN BHD</t>
+          <t>PERUMAHAN MASTERON SDN BHD</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>661</v>
+        <v>551</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0</v>
@@ -2720,36 +2603,100 @@
         <f>F15/$E$15</f>
         <v/>
       </c>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="9" t="n"/>
-      <c r="O15" s="9" t="n"/>
-      <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="9" t="n"/>
-      <c r="S15" s="10" t="n"/>
-      <c r="T15" s="9" t="n"/>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="10" t="n"/>
-      <c r="W15" s="9" t="n"/>
-      <c r="X15" s="9" t="n"/>
-      <c r="Y15" s="10" t="n"/>
-      <c r="Z15" s="9" t="n"/>
-      <c r="AA15" s="9" t="n"/>
-      <c r="AB15" s="10" t="n"/>
-      <c r="AC15" s="9" t="n"/>
-      <c r="AD15" s="9" t="n"/>
-      <c r="AE15" s="10" t="n"/>
+      <c r="H15" s="9">
+        <f>I15-F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10">
+        <f>I15/$E$15</f>
+        <v/>
+      </c>
+      <c r="K15" s="9">
+        <f>L15-I15</f>
+        <v/>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10">
+        <f>L15/$E$15</f>
+        <v/>
+      </c>
+      <c r="N15" s="9">
+        <f>O15-L15</f>
+        <v/>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="10">
+        <f>O15/$E$15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="9">
+        <f>R15-O15</f>
+        <v/>
+      </c>
+      <c r="R15" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="S15" s="10">
+        <f>R15/$E$15</f>
+        <v/>
+      </c>
+      <c r="T15" s="9">
+        <f>U15-R15</f>
+        <v/>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="V15" s="10">
+        <f>U15/$E$15</f>
+        <v/>
+      </c>
+      <c r="W15" s="9">
+        <f>X15-U15</f>
+        <v/>
+      </c>
+      <c r="X15" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="Y15" s="10">
+        <f>X15/$E$15</f>
+        <v/>
+      </c>
+      <c r="Z15" s="9">
+        <f>AA15-X15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="AB15" s="10">
+        <f>AA15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="9">
+        <f>AD15-AA15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="AE15" s="10">
+        <f>AD15/$E$15</f>
+        <v/>
+      </c>
       <c r="AF15" s="9">
-        <f>AG15-F15</f>
+        <f>AG15-AD15</f>
         <v/>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>659</v>
+        <v>86</v>
       </c>
       <c r="AH15" s="10">
         <f>AG15/$E$15</f>
@@ -2760,7 +2707,7 @@
         <v/>
       </c>
       <c r="AJ15" s="9" t="n">
-        <v>659</v>
+        <v>96</v>
       </c>
       <c r="AK15" s="10">
         <f>AJ15/$E$15</f>
@@ -2771,7 +2718,7 @@
         <v/>
       </c>
       <c r="AM15" s="9" t="n">
-        <v>659</v>
+        <v>118</v>
       </c>
       <c r="AN15" s="10">
         <f>AM15/$E$15</f>
@@ -2782,7 +2729,7 @@
         <v/>
       </c>
       <c r="AP15" s="9" t="n">
-        <v>659</v>
+        <v>121</v>
       </c>
       <c r="AQ15" s="10">
         <f>AP15/$E$15</f>
@@ -2793,7 +2740,7 @@
         <v/>
       </c>
       <c r="AS15" s="9" t="n">
-        <v>659</v>
+        <v>121</v>
       </c>
       <c r="AT15" s="10">
         <f>AS15/$E$15</f>
@@ -2804,7 +2751,7 @@
         <v/>
       </c>
       <c r="AV15" s="11" t="n">
-        <v>659</v>
+        <v>124</v>
       </c>
       <c r="AW15" s="12">
         <f>AV15/$E$15</f>
@@ -2817,17 +2764,21 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>THE SHANG RESIDENCE</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
+          <t>RESIDENSI AURUM</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>30250-2</t>
+        </is>
+      </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>SHANG HEIGHT REALTY SDN. BHD.</t>
+          <t>AMBER HOMES SRI PETALING SDN BHD</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>449</v>
+        <v>661</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0</v>
@@ -2836,100 +2787,36 @@
         <f>F16/$E$16</f>
         <v/>
       </c>
-      <c r="H16" s="9">
-        <f>I16-F16</f>
-        <v/>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="10">
-        <f>I16/$E$16</f>
-        <v/>
-      </c>
-      <c r="K16" s="9">
-        <f>L16-I16</f>
-        <v/>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="10">
-        <f>L16/$E$16</f>
-        <v/>
-      </c>
-      <c r="N16" s="9">
-        <f>O16-L16</f>
-        <v/>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="10">
-        <f>O16/$E$16</f>
-        <v/>
-      </c>
-      <c r="Q16" s="9">
-        <f>R16-O16</f>
-        <v/>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="10">
-        <f>R16/$E$16</f>
-        <v/>
-      </c>
-      <c r="T16" s="9">
-        <f>U16-R16</f>
-        <v/>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="10">
-        <f>U16/$E$16</f>
-        <v/>
-      </c>
-      <c r="W16" s="9">
-        <f>X16-U16</f>
-        <v/>
-      </c>
-      <c r="X16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="10">
-        <f>X16/$E$16</f>
-        <v/>
-      </c>
-      <c r="Z16" s="9">
-        <f>AA16-X16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="10">
-        <f>AA16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AC16" s="9">
-        <f>AD16-AA16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="10">
-        <f>AD16/$E$16</f>
-        <v/>
-      </c>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="10" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="9" t="n"/>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="10" t="n"/>
+      <c r="AC16" s="9" t="n"/>
+      <c r="AD16" s="9" t="n"/>
+      <c r="AE16" s="10" t="n"/>
       <c r="AF16" s="9">
-        <f>AG16-AD16</f>
+        <f>AG16-F16</f>
         <v/>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="AH16" s="10">
         <f>AG16/$E$16</f>
@@ -2940,7 +2827,7 @@
         <v/>
       </c>
       <c r="AJ16" s="9" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="AK16" s="10">
         <f>AJ16/$E$16</f>
@@ -2951,7 +2838,7 @@
         <v/>
       </c>
       <c r="AM16" s="9" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="AN16" s="10">
         <f>AM16/$E$16</f>
@@ -2962,7 +2849,7 @@
         <v/>
       </c>
       <c r="AP16" s="9" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="AQ16" s="10">
         <f>AP16/$E$16</f>
@@ -2973,7 +2860,7 @@
         <v/>
       </c>
       <c r="AS16" s="9" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="AT16" s="10">
         <f>AS16/$E$16</f>
@@ -2984,12 +2871,75 @@
         <v/>
       </c>
       <c r="AV16" s="11" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="AW16" s="12">
         <f>AV16/$E$16</f>
         <v/>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>THE SHANG RESIDENCE</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>SHANG HEIGHT REALTY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>449</v>
+      </c>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="9" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="10" t="n"/>
+      <c r="AC17" s="9" t="n"/>
+      <c r="AD17" s="9" t="n"/>
+      <c r="AE17" s="10" t="n"/>
+      <c r="AF17" s="9" t="n"/>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="10" t="n"/>
+      <c r="AI17" s="9" t="n"/>
+      <c r="AJ17" s="9" t="n"/>
+      <c r="AK17" s="10" t="n"/>
+      <c r="AL17" s="9" t="n"/>
+      <c r="AM17" s="9" t="n"/>
+      <c r="AN17" s="10" t="n"/>
+      <c r="AO17" s="9" t="n"/>
+      <c r="AP17" s="9" t="n"/>
+      <c r="AQ17" s="10" t="n"/>
+      <c r="AR17" s="9" t="n"/>
+      <c r="AS17" s="9" t="n"/>
+      <c r="AT17" s="10" t="n"/>
+      <c r="AU17" s="11" t="n"/>
+      <c r="AV17" s="11" t="n"/>
+      <c r="AW17" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AW17"/>
+  <dimension ref="A2:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,9 @@
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
     <col width="9" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="9" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -594,8 +597,11 @@
       <c r="AR3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="AU3" s="4" t="n">
+      <c r="AU3" s="3" t="n">
         <v>46241</v>
+      </c>
+      <c r="AX3" s="4" t="n">
+        <v>46248</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -831,17 +837,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AU4" s="6" t="inlineStr">
+      <c r="AU4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="AV4" s="6" t="inlineStr">
+      <c r="AV4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AW4" s="6" t="inlineStr">
+      <c r="AW4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AX4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="AY4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AZ4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -910,9 +931,17 @@
       <c r="AR5" s="9" t="n"/>
       <c r="AS5" s="9" t="n"/>
       <c r="AT5" s="10" t="n"/>
-      <c r="AU5" s="11" t="n"/>
-      <c r="AV5" s="11" t="n"/>
-      <c r="AW5" s="12" t="n"/>
+      <c r="AU5" s="9" t="n"/>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="10" t="n"/>
+      <c r="AX5" s="11" t="n"/>
+      <c r="AY5" s="11" t="n">
+        <v>177</v>
+      </c>
+      <c r="AZ5" s="12">
+        <f>AY5/$E$5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1086,15 +1115,26 @@
         <f>AS6/$E$6</f>
         <v/>
       </c>
-      <c r="AU6" s="11">
+      <c r="AU6" s="9">
         <f>AV6-AS6</f>
         <v/>
       </c>
-      <c r="AV6" s="11" t="n">
+      <c r="AV6" s="9" t="n">
         <v>319</v>
       </c>
-      <c r="AW6" s="12">
+      <c r="AW6" s="10">
         <f>AV6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AX6" s="11">
+        <f>AY6-AV6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="11" t="n">
+        <v>334</v>
+      </c>
+      <c r="AZ6" s="12">
+        <f>AY6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1271,15 +1311,26 @@
         <f>AS7/$E$7</f>
         <v/>
       </c>
-      <c r="AU7" s="11">
+      <c r="AU7" s="9">
         <f>AV7-AS7</f>
         <v/>
       </c>
-      <c r="AV7" s="11" t="n">
+      <c r="AV7" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="AW7" s="12">
+      <c r="AW7" s="10">
         <f>AV7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AX7" s="11">
+        <f>AY7-AV7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="11" t="n">
+        <v>119</v>
+      </c>
+      <c r="AZ7" s="12">
+        <f>AY7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1455,15 +1506,26 @@
         <f>AS8/$E$8</f>
         <v/>
       </c>
-      <c r="AU8" s="11">
+      <c r="AU8" s="9">
         <f>AV8-AS8</f>
         <v/>
       </c>
-      <c r="AV8" s="11" t="n">
+      <c r="AV8" s="9" t="n">
         <v>985</v>
       </c>
-      <c r="AW8" s="12">
+      <c r="AW8" s="10">
         <f>AV8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AX8" s="11">
+        <f>AY8-AV8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="11" t="n">
+        <v>996</v>
+      </c>
+      <c r="AZ8" s="12">
+        <f>AY8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1640,15 +1702,26 @@
         <f>AS9/$E$9</f>
         <v/>
       </c>
-      <c r="AU9" s="11">
+      <c r="AU9" s="9">
         <f>AV9-AS9</f>
         <v/>
       </c>
-      <c r="AV9" s="11" t="n">
+      <c r="AV9" s="9" t="n">
         <v>1119</v>
       </c>
-      <c r="AW9" s="12">
+      <c r="AW9" s="10">
         <f>AV9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AX9" s="11">
+        <f>AY9-AV9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="11" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AZ9" s="12">
+        <f>AY9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -1825,15 +1898,26 @@
         <f>AS10/$E$10</f>
         <v/>
       </c>
-      <c r="AU10" s="11">
+      <c r="AU10" s="9">
         <f>AV10-AS10</f>
         <v/>
       </c>
-      <c r="AV10" s="11" t="n">
+      <c r="AV10" s="9" t="n">
         <v>491</v>
       </c>
-      <c r="AW10" s="12">
+      <c r="AW10" s="10">
         <f>AV10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AX10" s="11">
+        <f>AY10-AV10</f>
+        <v/>
+      </c>
+      <c r="AY10" s="11" t="n">
+        <v>499</v>
+      </c>
+      <c r="AZ10" s="12">
+        <f>AY10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2009,15 +2093,26 @@
         <f>AS11/$E$11</f>
         <v/>
       </c>
-      <c r="AU11" s="11">
+      <c r="AU11" s="9">
         <f>AV11-AS11</f>
         <v/>
       </c>
-      <c r="AV11" s="11" t="n">
+      <c r="AV11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AW11" s="12">
+      <c r="AW11" s="10">
         <f>AV11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AX11" s="11">
+        <f>AY11-AV11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="11" t="n">
+        <v>467</v>
+      </c>
+      <c r="AZ11" s="12">
+        <f>AY11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2193,15 +2288,26 @@
         <f>AS12/$E$12</f>
         <v/>
       </c>
-      <c r="AU12" s="11">
+      <c r="AU12" s="9">
         <f>AV12-AS12</f>
         <v/>
       </c>
-      <c r="AV12" s="11" t="n">
+      <c r="AV12" s="9" t="n">
         <v>235</v>
       </c>
-      <c r="AW12" s="12">
+      <c r="AW12" s="10">
         <f>AV12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AX12" s="11">
+        <f>AY12-AV12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="11" t="n">
+        <v>236</v>
+      </c>
+      <c r="AZ12" s="12">
+        <f>AY12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2378,15 +2484,26 @@
         <f>AS13/$E$13</f>
         <v/>
       </c>
-      <c r="AU13" s="11">
+      <c r="AU13" s="9">
         <f>AV13-AS13</f>
         <v/>
       </c>
-      <c r="AV13" s="11" t="n">
+      <c r="AV13" s="9" t="n">
         <v>608</v>
       </c>
-      <c r="AW13" s="12">
+      <c r="AW13" s="10">
         <f>AV13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AX13" s="11">
+        <f>AY13-AV13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="11" t="n">
+        <v>618</v>
+      </c>
+      <c r="AZ13" s="12">
+        <f>AY13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2562,15 +2679,26 @@
         <f>AS14/$E$14</f>
         <v/>
       </c>
-      <c r="AU14" s="11">
+      <c r="AU14" s="9">
         <f>AV14-AS14</f>
         <v/>
       </c>
-      <c r="AV14" s="11" t="n">
+      <c r="AV14" s="9" t="n">
         <v>1139</v>
       </c>
-      <c r="AW14" s="12">
+      <c r="AW14" s="10">
         <f>AV14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AX14" s="11">
+        <f>AY14-AV14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="11" t="n">
+        <v>1142</v>
+      </c>
+      <c r="AZ14" s="12">
+        <f>AY14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -2746,15 +2874,26 @@
         <f>AS15/$E$15</f>
         <v/>
       </c>
-      <c r="AU15" s="11">
+      <c r="AU15" s="9">
         <f>AV15-AS15</f>
         <v/>
       </c>
-      <c r="AV15" s="11" t="n">
+      <c r="AV15" s="9" t="n">
         <v>124</v>
       </c>
-      <c r="AW15" s="12">
+      <c r="AW15" s="10">
         <f>AV15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AX15" s="11">
+        <f>AY15-AV15</f>
+        <v/>
+      </c>
+      <c r="AY15" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="AZ15" s="12">
+        <f>AY15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -2866,15 +3005,26 @@
         <f>AS16/$E$16</f>
         <v/>
       </c>
-      <c r="AU16" s="11">
+      <c r="AU16" s="9">
         <f>AV16-AS16</f>
         <v/>
       </c>
-      <c r="AV16" s="11" t="n">
+      <c r="AV16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AW16" s="12">
+      <c r="AW16" s="10">
         <f>AV16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AX16" s="11">
+        <f>AY16-AV16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="11" t="n">
+        <v>659</v>
+      </c>
+      <c r="AZ16" s="12">
+        <f>AY16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -2937,12 +3087,15 @@
       <c r="AR17" s="9" t="n"/>
       <c r="AS17" s="9" t="n"/>
       <c r="AT17" s="10" t="n"/>
-      <c r="AU17" s="11" t="n"/>
-      <c r="AV17" s="11" t="n"/>
-      <c r="AW17" s="12" t="n"/>
+      <c r="AU17" s="9" t="n"/>
+      <c r="AV17" s="9" t="n"/>
+      <c r="AW17" s="10" t="n"/>
+      <c r="AX17" s="11" t="n"/>
+      <c r="AY17" s="11" t="n"/>
+      <c r="AZ17" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
     <mergeCell ref="W3:Y3"/>
@@ -2951,6 +3104,7 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="AC3:AE3"/>
     <mergeCell ref="AF3:AH3"/>
+    <mergeCell ref="AX3:AZ3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="Z3:AB3"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AZ17"/>
+  <dimension ref="A2:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3094,6 +3094,76 @@
       <c r="AY17" s="11" t="n"/>
       <c r="AZ17" s="12" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>BINASTRA COCHRANE</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>31332-1</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>BINASTRA SYNERGY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>830</v>
+      </c>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="9" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="9" t="n"/>
+      <c r="AD18" s="9" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="9" t="n"/>
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="10" t="n"/>
+      <c r="AI18" s="9" t="n"/>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="10" t="n"/>
+      <c r="AL18" s="9" t="n"/>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="10" t="n"/>
+      <c r="AO18" s="9" t="n"/>
+      <c r="AP18" s="9" t="n"/>
+      <c r="AQ18" s="10" t="n"/>
+      <c r="AR18" s="9" t="n"/>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="10" t="n"/>
+      <c r="AU18" s="9" t="n"/>
+      <c r="AV18" s="9" t="n"/>
+      <c r="AW18" s="10" t="n"/>
+      <c r="AX18" s="11" t="n"/>
+      <c r="AY18" s="11" t="n"/>
+      <c r="AZ18" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="F3:G3"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AZ18"/>
+  <dimension ref="A2:BC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -540,6 +540,9 @@
     <col width="9" customWidth="1" min="50" max="50"/>
     <col width="9" customWidth="1" min="51" max="51"/>
     <col width="9" customWidth="1" min="52" max="52"/>
+    <col width="9" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -600,8 +603,11 @@
       <c r="AU3" s="3" t="n">
         <v>46241</v>
       </c>
-      <c r="AX3" s="4" t="n">
+      <c r="AX3" s="3" t="n">
         <v>46248</v>
+      </c>
+      <c r="BA3" s="4" t="n">
+        <v>46255</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -852,17 +858,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AX4" s="6" t="inlineStr">
+      <c r="AX4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="AY4" s="6" t="inlineStr">
+      <c r="AY4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AZ4" s="6" t="inlineStr">
+      <c r="AZ4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BA4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BB4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BC4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -934,12 +955,23 @@
       <c r="AU5" s="9" t="n"/>
       <c r="AV5" s="9" t="n"/>
       <c r="AW5" s="10" t="n"/>
-      <c r="AX5" s="11" t="n"/>
-      <c r="AY5" s="11" t="n">
+      <c r="AX5" s="9" t="n"/>
+      <c r="AY5" s="9" t="n">
         <v>177</v>
       </c>
-      <c r="AZ5" s="12">
+      <c r="AZ5" s="10">
         <f>AY5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BA5" s="11">
+        <f>BB5-AY5</f>
+        <v/>
+      </c>
+      <c r="BB5" s="11" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC5" s="12">
+        <f>BB5/$E$5</f>
         <v/>
       </c>
     </row>
@@ -1126,15 +1158,26 @@
         <f>AV6/$E$6</f>
         <v/>
       </c>
-      <c r="AX6" s="11">
+      <c r="AX6" s="9">
         <f>AY6-AV6</f>
         <v/>
       </c>
-      <c r="AY6" s="11" t="n">
+      <c r="AY6" s="9" t="n">
         <v>334</v>
       </c>
-      <c r="AZ6" s="12">
+      <c r="AZ6" s="10">
         <f>AY6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BA6" s="11">
+        <f>BB6-AY6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="11" t="n">
+        <v>344</v>
+      </c>
+      <c r="BC6" s="12">
+        <f>BB6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1322,15 +1365,26 @@
         <f>AV7/$E$7</f>
         <v/>
       </c>
-      <c r="AX7" s="11">
+      <c r="AX7" s="9">
         <f>AY7-AV7</f>
         <v/>
       </c>
-      <c r="AY7" s="11" t="n">
+      <c r="AY7" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="AZ7" s="12">
+      <c r="AZ7" s="10">
         <f>AY7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BA7" s="11">
+        <f>BB7-AY7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="BC7" s="12">
+        <f>BB7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1517,15 +1571,26 @@
         <f>AV8/$E$8</f>
         <v/>
       </c>
-      <c r="AX8" s="11">
+      <c r="AX8" s="9">
         <f>AY8-AV8</f>
         <v/>
       </c>
-      <c r="AY8" s="11" t="n">
+      <c r="AY8" s="9" t="n">
         <v>996</v>
       </c>
-      <c r="AZ8" s="12">
+      <c r="AZ8" s="10">
         <f>AY8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BA8" s="11">
+        <f>BB8-AY8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="11" t="n">
+        <v>1003</v>
+      </c>
+      <c r="BC8" s="12">
+        <f>BB8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1713,15 +1778,26 @@
         <f>AV9/$E$9</f>
         <v/>
       </c>
-      <c r="AX9" s="11">
+      <c r="AX9" s="9">
         <f>AY9-AV9</f>
         <v/>
       </c>
-      <c r="AY9" s="11" t="n">
+      <c r="AY9" s="9" t="n">
         <v>1125</v>
       </c>
-      <c r="AZ9" s="12">
+      <c r="AZ9" s="10">
         <f>AY9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BA9" s="11">
+        <f>BB9-AY9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="11" t="n">
+        <v>1125</v>
+      </c>
+      <c r="BC9" s="12">
+        <f>BB9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -1909,15 +1985,26 @@
         <f>AV10/$E$10</f>
         <v/>
       </c>
-      <c r="AX10" s="11">
+      <c r="AX10" s="9">
         <f>AY10-AV10</f>
         <v/>
       </c>
-      <c r="AY10" s="11" t="n">
+      <c r="AY10" s="9" t="n">
         <v>499</v>
       </c>
-      <c r="AZ10" s="12">
+      <c r="AZ10" s="10">
         <f>AY10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BA10" s="11">
+        <f>BB10-AY10</f>
+        <v/>
+      </c>
+      <c r="BB10" s="11" t="n">
+        <v>509</v>
+      </c>
+      <c r="BC10" s="12">
+        <f>BB10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2104,15 +2191,26 @@
         <f>AV11/$E$11</f>
         <v/>
       </c>
-      <c r="AX11" s="11">
+      <c r="AX11" s="9">
         <f>AY11-AV11</f>
         <v/>
       </c>
-      <c r="AY11" s="11" t="n">
+      <c r="AY11" s="9" t="n">
         <v>467</v>
       </c>
-      <c r="AZ11" s="12">
+      <c r="AZ11" s="10">
         <f>AY11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BA11" s="11">
+        <f>BB11-AY11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="11" t="n">
+        <v>467</v>
+      </c>
+      <c r="BC11" s="12">
+        <f>BB11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2299,15 +2397,26 @@
         <f>AV12/$E$12</f>
         <v/>
       </c>
-      <c r="AX12" s="11">
+      <c r="AX12" s="9">
         <f>AY12-AV12</f>
         <v/>
       </c>
-      <c r="AY12" s="11" t="n">
+      <c r="AY12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AZ12" s="12">
+      <c r="AZ12" s="10">
         <f>AY12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BA12" s="11">
+        <f>BB12-AY12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="11" t="n">
+        <v>236</v>
+      </c>
+      <c r="BC12" s="12">
+        <f>BB12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2495,15 +2604,26 @@
         <f>AV13/$E$13</f>
         <v/>
       </c>
-      <c r="AX13" s="11">
+      <c r="AX13" s="9">
         <f>AY13-AV13</f>
         <v/>
       </c>
-      <c r="AY13" s="11" t="n">
+      <c r="AY13" s="9" t="n">
         <v>618</v>
       </c>
-      <c r="AZ13" s="12">
+      <c r="AZ13" s="10">
         <f>AY13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BA13" s="11">
+        <f>BB13-AY13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="11" t="n">
+        <v>626</v>
+      </c>
+      <c r="BC13" s="12">
+        <f>BB13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2690,15 +2810,26 @@
         <f>AV14/$E$14</f>
         <v/>
       </c>
-      <c r="AX14" s="11">
+      <c r="AX14" s="9">
         <f>AY14-AV14</f>
         <v/>
       </c>
-      <c r="AY14" s="11" t="n">
+      <c r="AY14" s="9" t="n">
         <v>1142</v>
       </c>
-      <c r="AZ14" s="12">
+      <c r="AZ14" s="10">
         <f>AY14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BA14" s="11">
+        <f>BB14-AY14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="11" t="n">
+        <v>1151</v>
+      </c>
+      <c r="BC14" s="12">
+        <f>BB14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -2885,15 +3016,26 @@
         <f>AV15/$E$15</f>
         <v/>
       </c>
-      <c r="AX15" s="11">
+      <c r="AX15" s="9">
         <f>AY15-AV15</f>
         <v/>
       </c>
-      <c r="AY15" s="11" t="n">
+      <c r="AY15" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="AZ15" s="12">
+      <c r="AZ15" s="10">
         <f>AY15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BA15" s="11">
+        <f>BB15-AY15</f>
+        <v/>
+      </c>
+      <c r="BB15" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="BC15" s="12">
+        <f>BB15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -3016,15 +3158,26 @@
         <f>AV16/$E$16</f>
         <v/>
       </c>
-      <c r="AX16" s="11">
+      <c r="AX16" s="9">
         <f>AY16-AV16</f>
         <v/>
       </c>
-      <c r="AY16" s="11" t="n">
+      <c r="AY16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AZ16" s="12">
+      <c r="AZ16" s="10">
         <f>AY16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BA16" s="11">
+        <f>BB16-AY16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="11" t="n">
+        <v>659</v>
+      </c>
+      <c r="BC16" s="12">
+        <f>BB16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -3090,9 +3243,12 @@
       <c r="AU17" s="9" t="n"/>
       <c r="AV17" s="9" t="n"/>
       <c r="AW17" s="10" t="n"/>
-      <c r="AX17" s="11" t="n"/>
-      <c r="AY17" s="11" t="n"/>
-      <c r="AZ17" s="12" t="n"/>
+      <c r="AX17" s="9" t="n"/>
+      <c r="AY17" s="9" t="n"/>
+      <c r="AZ17" s="10" t="n"/>
+      <c r="BA17" s="11" t="n"/>
+      <c r="BB17" s="11" t="n"/>
+      <c r="BC17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3160,19 +3316,31 @@
       <c r="AU18" s="9" t="n"/>
       <c r="AV18" s="9" t="n"/>
       <c r="AW18" s="10" t="n"/>
-      <c r="AX18" s="11" t="n"/>
-      <c r="AY18" s="11" t="n">
+      <c r="AX18" s="9" t="n"/>
+      <c r="AY18" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="AZ18" s="12">
+      <c r="AZ18" s="10">
         <f>AY18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BA18" s="11">
+        <f>BB18-AY18</f>
+        <v/>
+      </c>
+      <c r="BB18" s="11" t="n">
+        <v>191</v>
+      </c>
+      <c r="BC18" s="12">
+        <f>BB18/$E$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
+    <mergeCell ref="BA3:BC3"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="AR3:AT3"/>
     <mergeCell ref="AI3:AK3"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>ARTE STAR 
+          <t>ARTE STAR
 MILANO</t>
         </is>
       </c>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BC18"/>
+  <dimension ref="A2:BF18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -543,6 +543,9 @@
     <col width="9" customWidth="1" min="53" max="53"/>
     <col width="9" customWidth="1" min="54" max="54"/>
     <col width="9" customWidth="1" min="55" max="55"/>
+    <col width="9" customWidth="1" min="56" max="56"/>
+    <col width="9" customWidth="1" min="57" max="57"/>
+    <col width="9" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -606,8 +609,11 @@
       <c r="AX3" s="3" t="n">
         <v>46248</v>
       </c>
-      <c r="BA3" s="4" t="n">
+      <c r="BA3" s="3" t="n">
         <v>46255</v>
+      </c>
+      <c r="BD3" s="4" t="n">
+        <v>46262</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -873,17 +879,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BA4" s="6" t="inlineStr">
+      <c r="BA4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BB4" s="6" t="inlineStr">
+      <c r="BB4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BC4" s="6" t="inlineStr">
+      <c r="BC4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BD4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BE4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BF4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -963,15 +984,26 @@
         <f>AY5/$E$5</f>
         <v/>
       </c>
-      <c r="BA5" s="11">
+      <c r="BA5" s="9">
         <f>BB5-AY5</f>
         <v/>
       </c>
-      <c r="BB5" s="11" t="n">
+      <c r="BB5" s="9" t="n">
         <v>183</v>
       </c>
-      <c r="BC5" s="12">
+      <c r="BC5" s="10">
         <f>BB5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BD5" s="11">
+        <f>BE5-BB5</f>
+        <v/>
+      </c>
+      <c r="BE5" s="11" t="n">
+        <v>186</v>
+      </c>
+      <c r="BF5" s="12">
+        <f>BE5/$E$5</f>
         <v/>
       </c>
     </row>
@@ -1169,15 +1201,26 @@
         <f>AY6/$E$6</f>
         <v/>
       </c>
-      <c r="BA6" s="11">
+      <c r="BA6" s="9">
         <f>BB6-AY6</f>
         <v/>
       </c>
-      <c r="BB6" s="11" t="n">
+      <c r="BB6" s="9" t="n">
         <v>344</v>
       </c>
-      <c r="BC6" s="12">
+      <c r="BC6" s="10">
         <f>BB6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BD6" s="11">
+        <f>BE6-BB6</f>
+        <v/>
+      </c>
+      <c r="BE6" s="11" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF6" s="12">
+        <f>BE6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1376,15 +1419,26 @@
         <f>AY7/$E$7</f>
         <v/>
       </c>
-      <c r="BA7" s="11">
+      <c r="BA7" s="9">
         <f>BB7-AY7</f>
         <v/>
       </c>
-      <c r="BB7" s="11" t="n">
+      <c r="BB7" s="9" t="n">
         <v>123</v>
       </c>
-      <c r="BC7" s="12">
+      <c r="BC7" s="10">
         <f>BB7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BD7" s="11">
+        <f>BE7-BB7</f>
+        <v/>
+      </c>
+      <c r="BE7" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="BF7" s="12">
+        <f>BE7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1582,15 +1636,26 @@
         <f>AY8/$E$8</f>
         <v/>
       </c>
-      <c r="BA8" s="11">
+      <c r="BA8" s="9">
         <f>BB8-AY8</f>
         <v/>
       </c>
-      <c r="BB8" s="11" t="n">
+      <c r="BB8" s="9" t="n">
         <v>1003</v>
       </c>
-      <c r="BC8" s="12">
+      <c r="BC8" s="10">
         <f>BB8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BD8" s="11">
+        <f>BE8-BB8</f>
+        <v/>
+      </c>
+      <c r="BE8" s="11" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BF8" s="12">
+        <f>BE8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1789,15 +1854,26 @@
         <f>AY9/$E$9</f>
         <v/>
       </c>
-      <c r="BA9" s="11">
+      <c r="BA9" s="9">
         <f>BB9-AY9</f>
         <v/>
       </c>
-      <c r="BB9" s="11" t="n">
+      <c r="BB9" s="9" t="n">
         <v>1125</v>
       </c>
-      <c r="BC9" s="12">
+      <c r="BC9" s="10">
         <f>BB9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BD9" s="11">
+        <f>BE9-BB9</f>
+        <v/>
+      </c>
+      <c r="BE9" s="11" t="n">
+        <v>1126</v>
+      </c>
+      <c r="BF9" s="12">
+        <f>BE9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -1996,15 +2072,26 @@
         <f>AY10/$E$10</f>
         <v/>
       </c>
-      <c r="BA10" s="11">
+      <c r="BA10" s="9">
         <f>BB10-AY10</f>
         <v/>
       </c>
-      <c r="BB10" s="11" t="n">
+      <c r="BB10" s="9" t="n">
         <v>509</v>
       </c>
-      <c r="BC10" s="12">
+      <c r="BC10" s="10">
         <f>BB10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BD10" s="11">
+        <f>BE10-BB10</f>
+        <v/>
+      </c>
+      <c r="BE10" s="11" t="n">
+        <v>517</v>
+      </c>
+      <c r="BF10" s="12">
+        <f>BE10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2202,15 +2289,26 @@
         <f>AY11/$E$11</f>
         <v/>
       </c>
-      <c r="BA11" s="11">
+      <c r="BA11" s="9">
         <f>BB11-AY11</f>
         <v/>
       </c>
-      <c r="BB11" s="11" t="n">
+      <c r="BB11" s="9" t="n">
         <v>467</v>
       </c>
-      <c r="BC11" s="12">
+      <c r="BC11" s="10">
         <f>BB11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BD11" s="11">
+        <f>BE11-BB11</f>
+        <v/>
+      </c>
+      <c r="BE11" s="11" t="n">
+        <v>467</v>
+      </c>
+      <c r="BF11" s="12">
+        <f>BE11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2408,15 +2506,26 @@
         <f>AY12/$E$12</f>
         <v/>
       </c>
-      <c r="BA12" s="11">
+      <c r="BA12" s="9">
         <f>BB12-AY12</f>
         <v/>
       </c>
-      <c r="BB12" s="11" t="n">
+      <c r="BB12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="BC12" s="12">
+      <c r="BC12" s="10">
         <f>BB12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BD12" s="11">
+        <f>BE12-BB12</f>
+        <v/>
+      </c>
+      <c r="BE12" s="11" t="n">
+        <v>237</v>
+      </c>
+      <c r="BF12" s="12">
+        <f>BE12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2615,15 +2724,26 @@
         <f>AY13/$E$13</f>
         <v/>
       </c>
-      <c r="BA13" s="11">
+      <c r="BA13" s="9">
         <f>BB13-AY13</f>
         <v/>
       </c>
-      <c r="BB13" s="11" t="n">
+      <c r="BB13" s="9" t="n">
         <v>626</v>
       </c>
-      <c r="BC13" s="12">
+      <c r="BC13" s="10">
         <f>BB13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BD13" s="11">
+        <f>BE13-BB13</f>
+        <v/>
+      </c>
+      <c r="BE13" s="11" t="n">
+        <v>642</v>
+      </c>
+      <c r="BF13" s="12">
+        <f>BE13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2821,15 +2941,26 @@
         <f>AY14/$E$14</f>
         <v/>
       </c>
-      <c r="BA14" s="11">
+      <c r="BA14" s="9">
         <f>BB14-AY14</f>
         <v/>
       </c>
-      <c r="BB14" s="11" t="n">
+      <c r="BB14" s="9" t="n">
         <v>1151</v>
       </c>
-      <c r="BC14" s="12">
+      <c r="BC14" s="10">
         <f>BB14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BD14" s="11">
+        <f>BE14-BB14</f>
+        <v/>
+      </c>
+      <c r="BE14" s="11" t="n">
+        <v>1155</v>
+      </c>
+      <c r="BF14" s="12">
+        <f>BE14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -3027,15 +3158,26 @@
         <f>AY15/$E$15</f>
         <v/>
       </c>
-      <c r="BA15" s="11">
+      <c r="BA15" s="9">
         <f>BB15-AY15</f>
         <v/>
       </c>
-      <c r="BB15" s="11" t="n">
+      <c r="BB15" s="9" t="n">
         <v>127</v>
       </c>
-      <c r="BC15" s="12">
+      <c r="BC15" s="10">
         <f>BB15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BD15" s="11">
+        <f>BE15-BB15</f>
+        <v/>
+      </c>
+      <c r="BE15" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="BF15" s="12">
+        <f>BE15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -3169,15 +3311,26 @@
         <f>AY16/$E$16</f>
         <v/>
       </c>
-      <c r="BA16" s="11">
+      <c r="BA16" s="9">
         <f>BB16-AY16</f>
         <v/>
       </c>
-      <c r="BB16" s="11" t="n">
+      <c r="BB16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BC16" s="12">
+      <c r="BC16" s="10">
         <f>BB16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BD16" s="11">
+        <f>BE16-BB16</f>
+        <v/>
+      </c>
+      <c r="BE16" s="11" t="n">
+        <v>659</v>
+      </c>
+      <c r="BF16" s="12">
+        <f>BE16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -3246,9 +3399,12 @@
       <c r="AX17" s="9" t="n"/>
       <c r="AY17" s="9" t="n"/>
       <c r="AZ17" s="10" t="n"/>
-      <c r="BA17" s="11" t="n"/>
-      <c r="BB17" s="11" t="n"/>
-      <c r="BC17" s="12" t="n"/>
+      <c r="BA17" s="9" t="n"/>
+      <c r="BB17" s="9" t="n"/>
+      <c r="BC17" s="10" t="n"/>
+      <c r="BD17" s="11" t="n"/>
+      <c r="BE17" s="11" t="n"/>
+      <c r="BF17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3324,20 +3480,31 @@
         <f>AY18/$E$18</f>
         <v/>
       </c>
-      <c r="BA18" s="11">
+      <c r="BA18" s="9">
         <f>BB18-AY18</f>
         <v/>
       </c>
-      <c r="BB18" s="11" t="n">
+      <c r="BB18" s="9" t="n">
         <v>191</v>
       </c>
-      <c r="BC18" s="12">
+      <c r="BC18" s="10">
         <f>BB18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BD18" s="11">
+        <f>BE18-BB18</f>
+        <v/>
+      </c>
+      <c r="BE18" s="11" t="n">
+        <v>246</v>
+      </c>
+      <c r="BF18" s="12">
+        <f>BE18/$E$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
     <mergeCell ref="BA3:BC3"/>
@@ -3354,6 +3521,7 @@
     <mergeCell ref="AL3:AN3"/>
     <mergeCell ref="AO3:AQ3"/>
     <mergeCell ref="N3:P3"/>
+    <mergeCell ref="BD3:BF3"/>
     <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -1000,7 +1000,7 @@
         <v/>
       </c>
       <c r="BE5" s="11" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="BF5" s="12">
         <f>BE5/$E$5</f>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="BE6" s="11" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="BF6" s="12">
         <f>BE6/$E$6</f>
@@ -1435,7 +1435,7 @@
         <v/>
       </c>
       <c r="BE7" s="11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF7" s="12">
         <f>BE7/$E$7</f>
@@ -2088,7 +2088,7 @@
         <v/>
       </c>
       <c r="BE10" s="11" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="BF10" s="12">
         <f>BE10/$E$10</f>
@@ -2740,7 +2740,7 @@
         <v/>
       </c>
       <c r="BE13" s="11" t="n">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="BF13" s="12">
         <f>BE13/$E$13</f>
@@ -2957,7 +2957,7 @@
         <v/>
       </c>
       <c r="BE14" s="11" t="n">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="BF14" s="12">
         <f>BE14/$E$14</f>
@@ -3174,7 +3174,7 @@
         <v/>
       </c>
       <c r="BE15" s="11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BF15" s="12">
         <f>BE15/$E$15</f>
@@ -3496,7 +3496,7 @@
         <v/>
       </c>
       <c r="BE18" s="11" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="BF18" s="12">
         <f>BE18/$E$18</f>

--- a/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
+++ b/docs/downloads/Tduh_Developer_Project_Sales_Status.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BG18"/>
+  <dimension ref="A2:BJ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -550,6 +550,9 @@
     <col width="9" customWidth="1" min="57" max="57"/>
     <col width="9" customWidth="1" min="58" max="58"/>
     <col width="9" customWidth="1" min="59" max="59"/>
+    <col width="9" customWidth="1" min="60" max="60"/>
+    <col width="9" customWidth="1" min="61" max="61"/>
+    <col width="9" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -616,8 +619,11 @@
       <c r="BB3" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BE3" s="3" t="n">
         <v>46262</v>
+      </c>
+      <c r="BH3" s="4" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -904,17 +910,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BE4" s="6" t="inlineStr">
+      <c r="BE4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BF4" s="6" t="inlineStr">
+      <c r="BF4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BG4" s="6" t="inlineStr">
+      <c r="BG4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BH4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BI4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BJ4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1008,15 +1029,26 @@
         <f>BC5/$D$5</f>
         <v/>
       </c>
-      <c r="BE5" s="12">
+      <c r="BE5" s="10">
         <f>BF5-BC5</f>
         <v/>
       </c>
-      <c r="BF5" s="12" t="n">
+      <c r="BF5" s="10" t="n">
         <v>188</v>
       </c>
-      <c r="BG5" s="13">
+      <c r="BG5" s="11">
         <f>BF5/$D$5</f>
+        <v/>
+      </c>
+      <c r="BH5" s="12">
+        <f>BI5-BF5</f>
+        <v/>
+      </c>
+      <c r="BI5" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="BJ5" s="13">
+        <f>BI5/$D$5</f>
         <v/>
       </c>
     </row>
@@ -1228,15 +1260,26 @@
         <f>BC6/$D$6</f>
         <v/>
       </c>
-      <c r="BE6" s="12">
+      <c r="BE6" s="10">
         <f>BF6-BC6</f>
         <v/>
       </c>
-      <c r="BF6" s="12" t="n">
+      <c r="BF6" s="10" t="n">
         <v>355</v>
       </c>
-      <c r="BG6" s="13">
+      <c r="BG6" s="11">
         <f>BF6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BH6" s="12">
+        <f>BI6-BF6</f>
+        <v/>
+      </c>
+      <c r="BI6" s="12" t="n">
+        <v>365</v>
+      </c>
+      <c r="BJ6" s="13">
+        <f>BI6/$D$6</f>
         <v/>
       </c>
     </row>
@@ -1449,15 +1492,26 @@
         <f>BC7/$D$7</f>
         <v/>
       </c>
-      <c r="BE7" s="12">
+      <c r="BE7" s="10">
         <f>BF7-BC7</f>
         <v/>
       </c>
-      <c r="BF7" s="12" t="n">
+      <c r="BF7" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="BG7" s="13">
+      <c r="BG7" s="11">
         <f>BF7/$D$7</f>
+        <v/>
+      </c>
+      <c r="BH7" s="12">
+        <f>BI7-BF7</f>
+        <v/>
+      </c>
+      <c r="BI7" s="12" t="n">
+        <v>131</v>
+      </c>
+      <c r="BJ7" s="13">
+        <f>BI7/$D$7</f>
         <v/>
       </c>
     </row>
@@ -1669,15 +1723,26 @@
         <f>BC8/$D$8</f>
         <v/>
       </c>
-      <c r="BE8" s="12">
+      <c r="BE8" s="10">
         <f>BF8-BC8</f>
         <v/>
       </c>
-      <c r="BF8" s="12" t="n">
+      <c r="BF8" s="10" t="n">
         <v>1009</v>
       </c>
-      <c r="BG8" s="13">
+      <c r="BG8" s="11">
         <f>BF8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BH8" s="12">
+        <f>BI8-BF8</f>
+        <v/>
+      </c>
+      <c r="BI8" s="12" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BJ8" s="13">
+        <f>BI8/$D$8</f>
         <v/>
       </c>
     </row>
@@ -1890,15 +1955,26 @@
         <f>BC9/$D$9</f>
         <v/>
       </c>
-      <c r="BE9" s="12">
+      <c r="BE9" s="10">
         <f>BF9-BC9</f>
         <v/>
       </c>
-      <c r="BF9" s="12" t="n">
+      <c r="BF9" s="10" t="n">
         <v>1126</v>
       </c>
-      <c r="BG9" s="13">
+      <c r="BG9" s="11">
         <f>BF9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BH9" s="12">
+        <f>BI9-BF9</f>
+        <v/>
+      </c>
+      <c r="BI9" s="12" t="n">
+        <v>1128</v>
+      </c>
+      <c r="BJ9" s="13">
+        <f>BI9/$D$9</f>
         <v/>
       </c>
     </row>
@@ -2111,15 +2187,26 @@
         <f>BC10/$D$10</f>
         <v/>
       </c>
-      <c r="BE10" s="12">
+      <c r="BE10" s="10">
         <f>BF10-BC10</f>
         <v/>
       </c>
-      <c r="BF10" s="12" t="n">
+      <c r="BF10" s="10" t="n">
         <v>519</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BG10" s="11">
         <f>BF10/$D$10</f>
+        <v/>
+      </c>
+      <c r="BH10" s="12">
+        <f>BI10-BF10</f>
+        <v/>
+      </c>
+      <c r="BI10" s="12" t="n">
+        <v>521</v>
+      </c>
+      <c r="BJ10" s="13">
+        <f>BI10/$D$10</f>
         <v/>
       </c>
     </row>
@@ -2331,15 +2418,26 @@
         <f>BC11/$D$11</f>
         <v/>
       </c>
-      <c r="BE11" s="12">
+      <c r="BE11" s="10">
         <f>BF11-BC11</f>
         <v/>
       </c>
-      <c r="BF11" s="12" t="n">
+      <c r="BF11" s="10" t="n">
         <v>467</v>
       </c>
-      <c r="BG11" s="13">
+      <c r="BG11" s="11">
         <f>BF11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BH11" s="12">
+        <f>BI11-BF11</f>
+        <v/>
+      </c>
+      <c r="BI11" s="12" t="n">
+        <v>469</v>
+      </c>
+      <c r="BJ11" s="13">
+        <f>BI11/$D$11</f>
         <v/>
       </c>
     </row>
@@ -2551,15 +2649,26 @@
         <f>BC12/$D$12</f>
         <v/>
       </c>
-      <c r="BE12" s="12">
+      <c r="BE12" s="10">
         <f>BF12-BC12</f>
         <v/>
       </c>
-      <c r="BF12" s="12" t="n">
+      <c r="BF12" s="10" t="n">
         <v>237</v>
       </c>
-      <c r="BG12" s="13">
+      <c r="BG12" s="11">
         <f>BF12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BH12" s="12">
+        <f>BI12-BF12</f>
+        <v/>
+      </c>
+      <c r="BI12" s="12" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ12" s="13">
+        <f>BI12/$D$12</f>
         <v/>
       </c>
     </row>
@@ -2772,15 +2881,26 @@
         <f>BC13/$D$13</f>
         <v/>
       </c>
-      <c r="BE13" s="12">
+      <c r="BE13" s="10">
         <f>BF13-BC13</f>
         <v/>
       </c>
-      <c r="BF13" s="12" t="n">
+      <c r="BF13" s="10" t="n">
         <v>647</v>
       </c>
-      <c r="BG13" s="13">
+      <c r="BG13" s="11">
         <f>BF13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BH13" s="12">
+        <f>BI13-BF13</f>
+        <v/>
+      </c>
+      <c r="BI13" s="12" t="n">
+        <v>653</v>
+      </c>
+      <c r="BJ13" s="13">
+        <f>BI13/$D$13</f>
         <v/>
       </c>
     </row>
@@ -2992,15 +3112,26 @@
         <f>BC14/$D$14</f>
         <v/>
       </c>
-      <c r="BE14" s="12">
+      <c r="BE14" s="10">
         <f>BF14-BC14</f>
         <v/>
       </c>
-      <c r="BF14" s="12" t="n">
+      <c r="BF14" s="10" t="n">
         <v>1157</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BG14" s="11">
         <f>BF14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BH14" s="12">
+        <f>BI14-BF14</f>
+        <v/>
+      </c>
+      <c r="BI14" s="12" t="n">
+        <v>1163</v>
+      </c>
+      <c r="BJ14" s="13">
+        <f>BI14/$D$14</f>
         <v/>
       </c>
     </row>
@@ -3212,15 +3343,26 @@
         <f>BC15/$D$15</f>
         <v/>
       </c>
-      <c r="BE15" s="12">
+      <c r="BE15" s="10">
         <f>BF15-BC15</f>
         <v/>
       </c>
-      <c r="BF15" s="12" t="n">
+      <c r="BF15" s="10" t="n">
         <v>134</v>
       </c>
-      <c r="BG15" s="13">
+      <c r="BG15" s="11">
         <f>BF15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BH15" s="12">
+        <f>BI15-BF15</f>
+        <v/>
+      </c>
+      <c r="BI15" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="BJ15" s="13">
+        <f>BI15/$D$15</f>
         <v/>
       </c>
     </row>
@@ -3368,15 +3510,26 @@
         <f>BC16/$D$16</f>
         <v/>
       </c>
-      <c r="BE16" s="12">
+      <c r="BE16" s="10">
         <f>BF16-BC16</f>
         <v/>
       </c>
-      <c r="BF16" s="12" t="n">
+      <c r="BF16" s="10" t="n">
         <v>659</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BG16" s="11">
         <f>BF16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BH16" s="12">
+        <f>BI16-BF16</f>
+        <v/>
+      </c>
+      <c r="BI16" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="BJ16" s="13">
+        <f>BI16/$D$16</f>
         <v/>
       </c>
     </row>
@@ -3449,9 +3602,12 @@
       <c r="BB17" s="10" t="n"/>
       <c r="BC17" s="10" t="n"/>
       <c r="BD17" s="11" t="n"/>
-      <c r="BE17" s="12" t="n"/>
-      <c r="BF17" s="12" t="n"/>
-      <c r="BG17" s="13" t="n"/>
+      <c r="BE17" s="10" t="n"/>
+      <c r="BF17" s="10" t="n"/>
+      <c r="BG17" s="11" t="n"/>
+      <c r="BH17" s="12" t="n"/>
+      <c r="BI17" s="12" t="n"/>
+      <c r="BJ17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3541,38 +3697,50 @@
         <f>BC18/$D$18</f>
         <v/>
       </c>
-      <c r="BE18" s="12">
+      <c r="BE18" s="10">
         <f>BF18-BC18</f>
         <v/>
       </c>
-      <c r="BF18" s="12" t="n">
+      <c r="BF18" s="10" t="n">
         <v>260</v>
       </c>
-      <c r="BG18" s="13">
+      <c r="BG18" s="11">
         <f>BF18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BH18" s="12">
+        <f>BI18-BF18</f>
+        <v/>
+      </c>
+      <c r="BI18" s="12" t="n">
+        <v>303</v>
+      </c>
+      <c r="BJ18" s="13">
+        <f>BI18/$D$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:W3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AP3:AR3"/>
+  <mergeCells count="19">
     <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="L3:N3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="BH3:BJ3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
